--- a/important_mails_2026-06-22.xlsx
+++ b/important_mails_2026-06-22.xlsx
@@ -2605,7 +2605,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2620,73 +2620,21 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 20:37:03 +0000</t>
+          <t>Sun, 21 Jun 2026 12:49:43 +0000</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Important message: your account is at risk of deactivation</t>
+          <t>Pagamento elaborato con successo</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>96
- 96
- Hello,
- Based on your Account Health Rating, your account is at risk of being deactivated. The Account Health Rating takes into account factors such as:
--
- The number of unresolved policy violations on your account at any given time
--
- The degree to which the violation negatively impacts the customer experience
--
- Whether the violation contravenes applicable laws and regulations
- We encourage you to address the violations on your Account Health page as soon as possible in order to prevent unnecessary disruption to your selling account.
- Why is this happening?
- There are unaddressed policy violations related to your selling account. It is your obligation to make sure that you adhere to Amazon’s policies. To learn more about the Account Health Rating and the policies within it, please visit the following: https://sellercentral.amazon.com/performance/dashboard?ref=ah_em_composite .
- What can I do to avoid account deactivation?
- Addressing policy violations on your Account Health page in a timely manner will prevent unnecessary disruption to your selling account. You can view the violations in the Policy Compliance section of the Account Health page https://sellercentral.amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 12:49:43 +0000</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Pagamento elaborato con successo</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2701,39 +2649,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 10:18:43 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -2754,39 +2702,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 10:02:13 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>最后机会：请于6月19日前提报 Prime Day 促销</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -2809,39 +2757,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 14:18:31 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -2861,39 +2809,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:14:39 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Soumettre les numéros d'enregistrement REP avant le 30 juin</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -2902,39 +2850,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 09:11:12 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Seller News: June 2026</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2954,40 +2902,40 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 17:13:19 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Get increased New Selection Program (2026) benefits starting July
  30</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
@@ -3001,39 +2949,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 00:29:05 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12891299002&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12891299002&lt;/p&gt;
@@ -3049,39 +2997,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:26:46 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3096,39 +3044,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:13:30 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -3145,39 +3093,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:12:43 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -3195,40 +3143,40 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:12:12 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -3246,39 +3194,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:08:19 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -3296,39 +3244,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:17:27 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -3367,39 +3315,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:16:32 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -3417,39 +3365,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:16:13 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, xiao jianming:
@@ -3467,40 +3415,40 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:15:21 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -3518,39 +3466,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:24 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Documents de sécurité des produits requis pour les garder actifs</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour xiao jianming,
@@ -3568,39 +3516,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 04:59:29 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -3624,39 +3572,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 03:24:34 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-02</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -3678,39 +3626,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 03:04:08 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Action Required: Transparency Barcode Required for Your Products</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello from Amazon Seller Services,
@@ -3726,39 +3674,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 16:22:55 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3779,39 +3727,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 15:05:28 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3832,39 +3780,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 14:33:45 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $94.16 in an attempt to settle your Amazon seller account balance.
@@ -3880,39 +3828,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 21:11:17 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3933,39 +3881,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 03:06:46 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3981,39 +3929,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 16:09:43 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (JKfyD/ypoS)</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4033,39 +3981,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 04:19:55 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (wrlLFrQcT3)</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4085,39 +4033,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 18:59:47 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2605311NRC)</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4137,39 +4085,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 16:46:32 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4190,39 +4138,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 03:33:45 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4238,39 +4186,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 05:07:33 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (MtDohxu3JK)</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4290,39 +4238,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 13:57:10 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (okvedC6bat)</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4342,39 +4290,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 08:40:44 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4390,39 +4338,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 19:29:32 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (260520getf)</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4447,39 +4395,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:43:35 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $143.78 in an attempt to settle your Amazon seller account balance.
@@ -4495,39 +4443,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 01:13:32 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq5h330940)</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4552,39 +4500,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 06:55:02 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7kDrHSJf1h)</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4604,39 +4552,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 03:26:42 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4652,39 +4600,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 13:57:34 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Iot4D83CtY)</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4704,39 +4652,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:24:03 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4756,39 +4704,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:23:28 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4805,39 +4753,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 13:35:44 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4857,39 +4805,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:28:40 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4909,39 +4857,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:24:36 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4958,39 +4906,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:24:04 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5010,39 +4958,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5062,39 +5010,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 12:54:19 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5114,39 +5062,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 15:13:12 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 42.71. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -5160,39 +5108,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:53:43 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5212,39 +5160,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:51:09 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5261,39 +5209,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 16:29:28 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Estimado vendedor:
  Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 90.75 con el fin de saldar tu cuenta de vendedor de Amazon.
@@ -5305,39 +5253,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:57:49 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5357,39 +5305,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:56:47 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5406,39 +5354,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:56:35 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5458,39 +5406,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 8 Jun 2026 14:05:53 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5510,39 +5458,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 13:51:46 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5562,39 +5510,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:50 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5614,39 +5562,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:46 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5663,39 +5611,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 15:15:46 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5715,39 +5663,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5764,39 +5712,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5816,39 +5764,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:36 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5868,39 +5816,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5920,39 +5868,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 14:37:25 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5969,39 +5917,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6021,39 +5969,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:43:44 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6073,39 +6021,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:42:27 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6125,39 +6073,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 14:51:20 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -6173,39 +6121,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 13:35:40 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6222,39 +6170,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 14:39:47 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6271,6 +6219,58 @@
 Thank you for selling in the Amazon Store,
 Amazon Services
 Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 20:37:03 +0000</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Important message: your account is at risk of deactivation</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>96
+ 96
+ Hello,
+ Based on your Account Health Rating, your account is at risk of being deactivated. The Account Health Rating takes into account factors such as:
+-
+ The number of unresolved policy violations on your account at any given time
+-
+ The degree to which the violation negatively impacts the customer experience
+-
+ Whether the violation contravenes applicable laws and regulations
+ We encourage you to address the violations on your Account Health page as soon as possible in order to prevent unnecessary disruption to your selling account.
+ Why is this happening?
+ There are unaddressed policy violations related to your selling account. It is your obligation to make sure that you adhere to Amazon’s policies. To learn more about the Account Health Rating and the policies within it, please visit the following: https://sellercentral.amazon.com/performance/dashboard?ref=ah_em_composite .
+ What can I do to avoid account deactivation?
+ Addressing policy violations on your Account Health page in a timely manner will prevent unnecessary disruption to your selling account. You can view the violations in the Policy Compliance section of the Account Health page https://sellercentral.amazon</t>
         </is>
       </c>
     </row>
